--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -2350,7 +2350,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -1185,7 +1185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="136">
   <si>
     <t>!Table</t>
   </si>
@@ -1403,45 +1403,6 @@
     <t>Costume</t>
   </si>
   <si>
-    <t>클레이모어</t>
-  </si>
-  <si>
-    <t>스컬클리버 투구</t>
-  </si>
-  <si>
-    <t>스펠레인저 후드</t>
-  </si>
-  <si>
-    <t>스컬클리버 갑옷</t>
-  </si>
-  <si>
-    <t>스펠레인저 로브</t>
-  </si>
-  <si>
-    <t>스컬클리버 장갑</t>
-  </si>
-  <si>
-    <t>스펠레인저 장갑</t>
-  </si>
-  <si>
-    <t>스컬클리버 신발</t>
-  </si>
-  <si>
-    <t>스펠레인저 신발</t>
-  </si>
-  <si>
-    <t>스컬클리버 반지</t>
-  </si>
-  <si>
-    <t>스펠레인저 반지</t>
-  </si>
-  <si>
-    <t>스컬클리버 목걸이</t>
-  </si>
-  <si>
-    <t>스펠레인저 목걸이</t>
-  </si>
-  <si>
     <t>ItemIcon_Gear_Greatsword</t>
   </si>
   <si>
@@ -1463,9 +1424,6 @@
     <t>ItemIcon_Gear_Amulet</t>
   </si>
   <si>
-    <t>대검</t>
-  </si>
-  <si>
     <t>원거리 목걸이 장신구</t>
   </si>
   <si>
@@ -1572,10 +1530,6 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>룬검</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>석궁</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1584,18 +1538,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>매그넘</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>크로스보우</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>룬소드</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemIcon_Gear_RuneSword</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1605,14 +1547,6 @@
   </si>
   <si>
     <t>!ItemGradeType</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 유물1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 유물2</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1749,6 +1683,70 @@
   </si>
   <si>
     <t>Consumable</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍검</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>룬소드</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 투구</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 후드</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 갑옷</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 로브</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 장갑</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 신발</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 반지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 반지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 목걸이</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 목걸이</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 유물</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 유물</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2350,7 +2348,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2382,10 +2380,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2393,15 +2391,15 @@
         <v>37</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2409,7 +2407,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2426,7 +2424,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2442,15 +2440,15 @@
         <v>32</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2458,7 +2456,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2466,7 +2464,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2474,23 +2472,23 @@
         <v>39</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2498,7 +2496,7 @@
         <v>41</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2506,7 +2504,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C19" s="16"/>
     </row>
@@ -2544,7 +2542,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>28</v>
@@ -2566,23 +2564,23 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C27" s="16"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +2598,7 @@
     <col min="1" max="1" width="9" style="10"/>
     <col min="2" max="2" width="12.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.375" style="1" bestFit="1" customWidth="1"/>
@@ -2638,10 +2636,10 @@
         <v>19</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -2672,10 +2670,10 @@
         <v>18</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="J3" s="14" t="s">
         <v>20</v>
@@ -2690,14 +2688,14 @@
       <c r="B4" s="1">
         <v>1010101001</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>14</v>
@@ -2706,10 +2704,10 @@
         <v>36</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J4" s="12">
         <v>1</v>
@@ -2723,14 +2721,14 @@
       <c r="B5" s="1">
         <v>1010101002</v>
       </c>
-      <c r="C5" t="s">
-        <v>99</v>
+      <c r="C5" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
@@ -2739,10 +2737,10 @@
         <v>36</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J5" s="12">
         <v>1</v>
@@ -2757,14 +2755,14 @@
       <c r="B6" s="1">
         <v>1010101003</v>
       </c>
-      <c r="C6" t="s">
-        <v>98</v>
+      <c r="C6" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
@@ -2773,10 +2771,10 @@
         <v>36</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J6" s="12">
         <v>1</v>
@@ -2791,14 +2789,14 @@
       <c r="B7" s="1">
         <v>1010101004</v>
       </c>
-      <c r="C7" t="s">
-        <v>97</v>
+      <c r="C7" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>14</v>
@@ -2807,10 +2805,10 @@
         <v>36</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J7" s="12">
         <v>1</v>
@@ -2825,13 +2823,13 @@
         <v>1010202001</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>14</v>
@@ -2840,10 +2838,10 @@
         <v>31</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J8" s="12">
         <v>1</v>
@@ -2858,13 +2856,13 @@
         <v>1010202002</v>
       </c>
       <c r="C9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>14</v>
@@ -2873,10 +2871,10 @@
         <v>31</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J9" s="12">
         <v>1</v>
@@ -2891,10 +2889,10 @@
         <v>1010203001</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>24</v>
@@ -2906,10 +2904,10 @@
         <v>31</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J10" s="12">
         <v>1</v>
@@ -2924,10 +2922,10 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>24</v>
@@ -2939,10 +2937,10 @@
         <v>31</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J11" s="12">
         <v>1</v>
@@ -2957,13 +2955,13 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>14</v>
@@ -2972,10 +2970,10 @@
         <v>31</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J12" s="12">
         <v>1</v>
@@ -2990,13 +2988,13 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>14</v>
@@ -3005,10 +3003,10 @@
         <v>31</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J13" s="12">
         <v>1</v>
@@ -3023,13 +3021,13 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>14</v>
@@ -3038,10 +3036,10 @@
         <v>31</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J14" s="12">
         <v>1</v>
@@ -3056,13 +3054,13 @@
         <v>1010205002</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>14</v>
@@ -3071,10 +3069,10 @@
         <v>31</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J15" s="12">
         <v>1</v>
@@ -3089,13 +3087,13 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>14</v>
@@ -3104,10 +3102,10 @@
         <v>32</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J16" s="12">
         <v>1</v>
@@ -3122,13 +3120,13 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>14</v>
@@ -3137,10 +3135,10 @@
         <v>32</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J17" s="12">
         <v>1</v>
@@ -3155,13 +3153,13 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>14</v>
@@ -3170,10 +3168,10 @@
         <v>32</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J18" s="12">
         <v>1</v>
@@ -3188,13 +3186,13 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>14</v>
@@ -3203,10 +3201,10 @@
         <v>32</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J19" s="12">
         <v>1</v>
@@ -3217,25 +3215,25 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J20" s="12">
         <v>1</v>
@@ -3246,25 +3244,25 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J21" s="12">
         <v>1</v>
@@ -3275,25 +3273,25 @@
         <v>1030300001</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
@@ -3301,13 +3299,13 @@
         <v>1030100001</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>38</v>
@@ -3316,7 +3314,7 @@
         <v>39</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I23" s="12"/>
     </row>
@@ -3325,13 +3323,13 @@
         <v>1030100002</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>38</v>
@@ -3340,7 +3338,7 @@
         <v>39</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I24" s="12"/>
     </row>
@@ -3349,13 +3347,13 @@
         <v>1030100003</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>38</v>
@@ -3364,7 +3362,7 @@
         <v>39</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="I25" s="12"/>
     </row>
@@ -3373,22 +3371,22 @@
         <v>1030200001</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>38</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="I26" s="12"/>
     </row>
@@ -3397,22 +3395,22 @@
         <v>1030200002</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>38</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I27" s="12"/>
     </row>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -1185,7 +1185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="138">
   <si>
     <t>!Table</t>
   </si>
@@ -1329,9 +1329,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>ItemIcon_Gear_Armor</t>
-  </si>
-  <si>
     <t>고급</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1403,27 +1400,6 @@
     <t>Costume</t>
   </si>
   <si>
-    <t>ItemIcon_Gear_Greatsword</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Pistols</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Helmet</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Gloves</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Boots</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Ring</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_Amulet</t>
-  </si>
-  <si>
     <t>원거리 목걸이 장신구</t>
   </si>
   <si>
@@ -1514,9 +1490,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>ItemIcon_Gear_Relic</t>
-  </si>
-  <si>
     <t>Grade</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1538,14 +1511,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>ItemIcon_Gear_RuneSword</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Gear_CrossBow</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>!ItemGradeType</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1555,10 +1520,6 @@
   </si>
   <si>
     <t>스킬 포인트 획득</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_SkillBook</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -1599,154 +1560,209 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
+    <t>재료 - 제작, 강화, 스킬 승급 등에 소모되는 재료 아이템</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모품 - 아이템 상자</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모품 - 소모성 아이템</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모품 - 물약</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>하급 회복 물약</t>
+  </si>
+  <si>
+    <t>체력을 소량 회복한다</t>
+  </si>
+  <si>
+    <t>상급 회복 물약</t>
+  </si>
+  <si>
+    <t>체력을 대량 회복한다</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>일정 시간 공격력이 증가한다</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>일반 상자</t>
+  </si>
+  <si>
+    <t>개봉하면 보상을 획득한다</t>
+  </si>
+  <si>
+    <t>Box</t>
+  </si>
+  <si>
+    <t>10연 상자</t>
+  </si>
+  <si>
+    <t>개봉하면 보상을 10회 획득한다</t>
+  </si>
+  <si>
+    <t>공격력 비약</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍검</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>룬소드</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 투구</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 후드</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 갑옷</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 로브</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 장갑</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 장갑</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철 신발</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 신발</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 반지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 반지</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 목걸이</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 목걸이</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 유물</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 유물</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>소모품 - 스킬포인트 획득</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>석궁</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Armor_1</t>
+  </si>
+  <si>
+    <t>ItemIcon_Amulet_1</t>
+  </si>
+  <si>
+    <t>ItemIcon_Relic_1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Ring_1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Boots_1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_1</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_2</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_3</t>
+  </si>
+  <si>
+    <t>ItemIcon_Weapon_4</t>
+  </si>
+  <si>
+    <t>ItemIcon_SkillBook</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Potion_HpSmall</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Potion_HpLarge</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Scroll_Atk</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Box_Normal</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Box_Multi</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Armor_2</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Boots_2</t>
+  </si>
+  <si>
     <t>ItemGradeType</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료 - 제작, 강화, 스킬 승급 등에 소모되는 재료 아이템</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>소모품 - 아이템 상자</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>소모품 - 스킬포인트 획득 재료</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumable</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>소모품 - 소모성 아이템</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>소모품 - 물약</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>하급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 소량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpSmall</t>
-  </si>
-  <si>
-    <t>상급 회복 물약</t>
-  </si>
-  <si>
-    <t>체력을 대량 회복한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Potion_HpLarge</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>일정 시간 공격력이 증가한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Scroll_Atk</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>일반 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Normal</t>
-  </si>
-  <si>
-    <t>Box</t>
-  </si>
-  <si>
-    <t>10연 상자</t>
-  </si>
-  <si>
-    <t>개봉하면 보상을 10회 획득한다</t>
-  </si>
-  <si>
-    <t>ItemIcon_Box_Multi</t>
-  </si>
-  <si>
-    <t>공격력 비약</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumable</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>쌍검</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>룬소드</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>강철 투구</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 후드</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>강철 갑옷</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 로브</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>강철 장갑</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 장갑</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>강철 신발</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>가죽 신발</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>근접 반지</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 반지</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>근접 목걸이</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 목걸이</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 유물</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>근접 유물</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2348,7 +2364,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2380,34 +2396,34 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2421,82 +2437,82 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2504,7 +2520,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="C19" s="16"/>
     </row>
@@ -2521,7 +2537,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2529,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2537,15 +2553,15 @@
         <v>10</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2553,7 +2569,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2564,23 +2580,23 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C27" s="16"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2612,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -2636,10 +2652,10 @@
         <v>19</v>
       </c>
       <c r="H2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>88</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -2670,10 +2686,10 @@
         <v>18</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J3" s="14" t="s">
         <v>20</v>
@@ -2689,25 +2705,25 @@
         <v>1010101001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J4" s="12">
         <v>1</v>
@@ -2722,25 +2738,25 @@
         <v>1010101002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J5" s="12">
         <v>1</v>
@@ -2756,25 +2772,25 @@
         <v>1010101003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J6" s="12">
         <v>1</v>
@@ -2790,25 +2806,25 @@
         <v>1010101004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J7" s="12">
         <v>1</v>
@@ -2823,25 +2839,25 @@
         <v>1010202001</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J8" s="12">
         <v>1</v>
@@ -2856,25 +2872,25 @@
         <v>1010202002</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J9" s="12">
         <v>1</v>
@@ -2889,25 +2905,25 @@
         <v>1010203001</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J10" s="12">
         <v>1</v>
@@ -2922,25 +2938,25 @@
         <v>1010203002</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J11" s="12">
         <v>1</v>
@@ -2955,25 +2971,25 @@
         <v>1010204001</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J12" s="12">
         <v>1</v>
@@ -2988,25 +3004,25 @@
         <v>1010204002</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J13" s="12">
         <v>1</v>
@@ -3021,25 +3037,25 @@
         <v>1010205001</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J14" s="12">
         <v>1</v>
@@ -3054,25 +3070,25 @@
         <v>1010205002</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J15" s="12">
         <v>1</v>
@@ -3087,25 +3103,25 @@
         <v>1010306001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J16" s="12">
         <v>1</v>
@@ -3120,25 +3136,25 @@
         <v>1010306002</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J17" s="12">
         <v>1</v>
@@ -3153,25 +3169,25 @@
         <v>1010307001</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J18" s="12">
         <v>1</v>
@@ -3186,25 +3202,25 @@
         <v>1010307002</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J19" s="12">
         <v>1</v>
@@ -3215,25 +3231,25 @@
         <v>1010408001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J20" s="12">
         <v>1</v>
@@ -3244,25 +3260,25 @@
         <v>1010408002</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J21" s="12">
         <v>1</v>
@@ -3273,25 +3289,25 @@
         <v>1030300001</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
@@ -3299,22 +3315,22 @@
         <v>1030100001</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="F23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H23" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I23" s="12"/>
     </row>
@@ -3323,22 +3339,22 @@
         <v>1030100002</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="F24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H24" s="12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="I24" s="12"/>
     </row>
@@ -3347,22 +3363,22 @@
         <v>1030100003</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H25" s="12" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="I25" s="12"/>
     </row>
@@ -3371,22 +3387,22 @@
         <v>1030200001</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I26" s="12"/>
     </row>
@@ -3395,22 +3411,22 @@
         <v>1030200002</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="I27" s="12"/>
     </row>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -1185,7 +1185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
   <si>
     <t>!Table</t>
   </si>
@@ -1763,6 +1763,14 @@
   </si>
   <si>
     <t>ItemGradeType</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessory</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2364,7 +2372,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3115,7 +3123,7 @@
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>70</v>
@@ -3372,7 +3380,7 @@
         <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>38</v>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -1185,7 +1185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="152">
   <si>
     <t>!Table</t>
   </si>
@@ -1771,6 +1771,52 @@
   </si>
   <si>
     <t>Accessory</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 강화 주문서</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구 강화 주문서</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 강화하는데 사용한다.</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구를 강화하는데 사용한다.</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>장신구를 강화하는데 사용한다.</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>장신구 강화 주문서</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_ArmorScroll</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_AccessoryScroll</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_WeaponScroll</t>
+  </si>
+  <si>
+    <t>Material</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2412,7 +2458,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>82</v>
@@ -2461,7 +2507,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>61</v>
@@ -2616,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -3293,121 +3339,124 @@
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>1030300001</v>
+      <c r="B22" s="1">
+        <v>1020200001</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>81</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I22" s="22"/>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
-        <v>1030100001</v>
+        <v>1020200002</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
-        <v>1030100002</v>
+        <v>1020200003</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="I24" s="22"/>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="1">
-        <v>1030100003</v>
+      <c r="B25">
+        <v>1030300001</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
-        <v>1030200001</v>
+        <v>1030100001</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>70</v>
@@ -3416,22 +3465,22 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
-        <v>1030200002</v>
+        <v>1030100002</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>91</v>
@@ -3439,29 +3488,84 @@
       <c r="I27" s="12"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="F28" s="12"/>
-      <c r="H28" s="12"/>
+      <c r="B28" s="1">
+        <v>1030100003</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>93</v>
+      </c>
       <c r="I28" s="12"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="F29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="B29" s="1">
+        <v>1030200001</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="I29" s="12"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="F30" s="12"/>
-      <c r="H30" s="12"/>
+      <c r="B30" s="1">
+        <v>1030200002</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="I30" s="12"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="F31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F32" s="12"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F33" s="12"/>
@@ -3492,6 +3596,21 @@
       <c r="F38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
+    </row>
+    <row r="39" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+    </row>
+    <row r="40" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="41" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>

--- a/Shared/XLS/Item.xlsx
+++ b/Shared/XLS/Item.xlsx
@@ -2418,7 +2418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
